--- a/data/stx_xlsx/AZN.ST.xlsx
+++ b/data/stx_xlsx/AZN.ST.xlsx
@@ -15088,8 +15088,14 @@
       <c r="R42" s="15">
         <v>42332.37</v>
       </c>
-      <c r="S42" s="15"/>
-      <c r="T42" s="15"/>
+      <c r="S42" s="15">
+        <f t="shared" ref="S42:T42" si="1">SUM(S43:S49)</f>
+        <v>48915.74</v>
+      </c>
+      <c r="T42" s="15">
+        <f t="shared" si="1"/>
+        <v>45097.15</v>
+      </c>
       <c r="U42" s="15">
         <v>46453.06</v>
       </c>
